--- a/data/extracted/inventory-receipts/REP CONTENEDOR BURDA HEAVY.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR BURDA HEAVY.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49130C16-F998-4D34-9BBB-100B2F9B821A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -983,7 +996,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -1024,12 +1037,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1309,50 +1321,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L207"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1390,12 +1402,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1433,7 +1445,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1471,7 +1483,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1509,7 +1521,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1547,7 +1559,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1585,7 +1597,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1623,7 +1635,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1661,7 +1673,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1699,7 +1711,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1737,7 +1749,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1775,7 +1787,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1813,7 +1825,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1851,7 +1863,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1889,7 +1901,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1927,7 +1939,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F21" s="1" t="s">
         <v>53</v>
       </c>
@@ -1947,7 +1959,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F22" s="1" t="s">
         <v>55</v>
       </c>
@@ -1967,7 +1979,7 @@
         <v>241.6</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -2005,7 +2017,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2043,7 +2055,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2081,7 +2093,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2119,7 +2131,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -2157,7 +2169,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -2195,7 +2207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -2233,7 +2245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -2271,7 +2283,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -2309,7 +2321,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -2347,7 +2359,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2385,7 +2397,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -2423,7 +2435,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -2461,7 +2473,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -2499,7 +2511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -2537,7 +2549,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -2575,7 +2587,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2613,7 +2625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -2651,7 +2663,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -2689,7 +2701,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -2727,7 +2739,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -2765,7 +2777,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -2803,7 +2815,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -2841,7 +2853,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -2879,7 +2891,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -2917,7 +2929,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -2955,7 +2967,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F49" s="1" t="s">
         <v>53</v>
       </c>
@@ -2975,7 +2987,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F50" s="1" t="s">
         <v>95</v>
       </c>
@@ -2995,7 +3007,7 @@
         <v>471.19999999999993</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -3033,7 +3045,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -3071,7 +3083,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -3109,7 +3121,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -3147,7 +3159,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -3185,7 +3197,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -3223,7 +3235,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -3261,7 +3273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -3299,7 +3311,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -3337,7 +3349,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -3375,7 +3387,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -3413,7 +3425,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -3451,7 +3463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -3489,7 +3501,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3527,7 +3539,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F65" s="1" t="s">
         <v>53</v>
       </c>
@@ -3547,7 +3559,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F66" s="1" t="s">
         <v>55</v>
       </c>
@@ -3567,7 +3579,7 @@
         <v>245.2</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -3605,7 +3617,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -3643,7 +3655,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -3681,7 +3693,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -3719,7 +3731,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -3757,7 +3769,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -3795,7 +3807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -3833,7 +3845,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -3871,7 +3883,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -3909,7 +3921,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -3947,7 +3959,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -3985,7 +3997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -4023,7 +4035,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -4061,7 +4073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -4099,7 +4111,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -4137,7 +4149,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -4175,7 +4187,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -4213,7 +4225,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -4251,7 +4263,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -4289,7 +4301,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -4327,7 +4339,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -4365,7 +4377,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -4403,7 +4415,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -4441,7 +4453,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -4479,7 +4491,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -4517,7 +4529,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -4555,7 +4567,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F93" s="1" t="s">
         <v>53</v>
       </c>
@@ -4575,7 +4587,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F94" s="1" t="s">
         <v>95</v>
       </c>
@@ -4598,7 +4610,7 @@
         <v>469.99999999999983</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -4636,7 +4648,7 @@
         <v>19.829999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -4674,7 +4686,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -4712,7 +4724,7 @@
         <v>20.14</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -4750,7 +4762,7 @@
         <v>19.72</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -4788,7 +4800,7 @@
         <v>20.07</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -4826,7 +4838,7 @@
         <v>19.920000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -4864,7 +4876,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -4902,7 +4914,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -4940,7 +4952,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -4978,7 +4990,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -5016,7 +5028,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -5054,7 +5066,7 @@
         <v>20.41</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -5092,7 +5104,7 @@
         <v>19.559999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -5130,7 +5142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -5168,7 +5180,7 @@
         <v>19.61</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -5206,7 +5218,7 @@
         <v>20.059999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -5244,7 +5256,7 @@
         <v>19.96</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -5282,7 +5294,7 @@
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -5320,7 +5332,7 @@
         <v>20.27</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -5358,7 +5370,7 @@
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -5396,7 +5408,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -5434,7 +5446,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -5472,7 +5484,7 @@
         <v>20.170000000000002</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -5510,7 +5522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -5548,7 +5560,7 @@
         <v>18.149999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -5586,7 +5598,7 @@
         <v>19.71</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -5624,7 +5636,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -5662,7 +5674,7 @@
         <v>19.98</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -5700,7 +5712,7 @@
         <v>18.510000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -5738,7 +5750,7 @@
         <v>20.02</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -5776,7 +5788,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -5814,7 +5826,7 @@
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -5852,7 +5864,7 @@
         <v>19.260000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -5890,7 +5902,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -5928,7 +5940,7 @@
         <v>20.420000000000002</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -5966,7 +5978,7 @@
         <v>20.03</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -6004,7 +6016,7 @@
         <v>19.93</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -6042,7 +6054,7 @@
         <v>20.16</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -6080,7 +6092,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -6118,7 +6130,7 @@
         <v>19.52</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -6156,7 +6168,7 @@
         <v>18.53</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -6194,7 +6206,7 @@
         <v>19.760000000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -6232,7 +6244,7 @@
         <v>19.93</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -6270,7 +6282,7 @@
         <v>19.579999999999998</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -6308,7 +6320,7 @@
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -6346,7 +6358,7 @@
         <v>19.489999999999998</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -6384,7 +6396,7 @@
         <v>19.71</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -6422,7 +6434,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -6460,7 +6472,7 @@
         <v>19.97</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -6498,7 +6510,7 @@
         <v>18.91</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -6536,7 +6548,7 @@
         <v>18.04</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -6574,7 +6586,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -6612,7 +6624,7 @@
         <v>19.66</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -6650,7 +6662,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -6688,7 +6700,7 @@
         <v>20.079999999999998</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -6726,7 +6738,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -6764,7 +6776,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -6802,7 +6814,7 @@
         <v>19.93</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -6840,7 +6852,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -6878,7 +6890,7 @@
         <v>19.329999999999998</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -6916,7 +6928,7 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -6954,7 +6966,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -6992,7 +7004,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -7030,7 +7042,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -7068,7 +7080,7 @@
         <v>20.28</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -7106,7 +7118,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -7144,7 +7156,7 @@
         <v>19.809999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -7182,7 +7194,7 @@
         <v>19.91</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -7220,7 +7232,7 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -7258,7 +7270,7 @@
         <v>19.809999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -7296,7 +7308,7 @@
         <v>19.97</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -7334,7 +7346,7 @@
         <v>19.010000000000002</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -7372,7 +7384,7 @@
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -7410,7 +7422,7 @@
         <v>20.04</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -7448,7 +7460,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -7486,7 +7498,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -7524,7 +7536,7 @@
         <v>19.79</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -7562,7 +7574,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -7600,7 +7612,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -7638,7 +7650,7 @@
         <v>19.170000000000002</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -7676,7 +7688,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -7714,7 +7726,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -7752,7 +7764,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -7790,7 +7802,7 @@
         <v>20.12</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -7828,7 +7840,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -7866,7 +7878,7 @@
         <v>19.68</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -7904,7 +7916,7 @@
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -7942,7 +7954,7 @@
         <v>19.66</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -7980,7 +7992,7 @@
         <v>19.63</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -8018,7 +8030,7 @@
         <v>19.63</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -8056,7 +8068,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -8094,7 +8106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -8132,7 +8144,7 @@
         <v>20.03</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -8170,7 +8182,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -8208,7 +8220,7 @@
         <v>17.89</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F190" s="1" t="s">
         <v>53</v>
       </c>
@@ -8228,7 +8240,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F191" s="1" t="s">
         <v>308</v>
       </c>
@@ -8245,7 +8257,7 @@
         <v>1871.6000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F192" s="1" t="s">
         <v>53</v>
       </c>
@@ -8265,7 +8277,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>310</v>
       </c>
@@ -8303,7 +8315,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F195" s="1" t="s">
         <v>53</v>
       </c>
@@ -8323,12 +8335,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K196" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>310</v>
       </c>
@@ -8366,7 +8378,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F198" s="1" t="s">
         <v>53</v>
       </c>
@@ -8386,12 +8398,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K199" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>310</v>
       </c>
@@ -8429,7 +8441,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F201" s="1" t="s">
         <v>53</v>
       </c>
@@ -8449,7 +8461,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>310</v>
       </c>
@@ -8487,7 +8499,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F204" s="1" t="s">
         <v>53</v>
       </c>
@@ -8507,12 +8519,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K205" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>310</v>
       </c>
@@ -8550,7 +8562,7 @@
         <v>250.77</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F207" s="1" t="s">
         <v>53</v>
       </c>
@@ -8574,4 +8586,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E813FB-D536-4B9A-816B-3ADED75C4E4C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>